--- a/AtchisonRegime/Outputs/Canada/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Canada/MSCI_Europe/df_regTrendSummaryMSCI_Europe.xlsx
@@ -1440,13 +1440,13 @@
         <v>45322</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F46" t="n">
-        <v>0.261158530922275</v>
+        <v>0.284261915209471</v>
       </c>
     </row>
   </sheetData>
